--- a/data/trans_orig/IP25A01_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25A01_2023-Estudios-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19252</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36408</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50352</t>
+          <t>50127</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72076</t>
+          <t>72393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24499</t>
+          <t>25694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40218</t>
+          <t>40426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29643</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18485</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39921</t>
+          <t>41413</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>28456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51836</t>
+          <t>50586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40169</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64314</t>
+          <t>64674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73662</t>
+          <t>75758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107340</t>
+          <t>107586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157864</t>
+          <t>158501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218938</t>
+          <t>218109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210701</t>
+          <t>209278</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259681</t>
+          <t>258504</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>387138</t>
+          <t>388866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>459327</t>
+          <t>462496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>178238</t>
+          <t>178371</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>255297</t>
+          <t>246932</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>198335</t>
+          <t>199336</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>248327</t>
+          <t>248359</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>390404</t>
+          <t>388347</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>477741</t>
+          <t>474742</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10983</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>23764</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>37498</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48142</t>
+          <t>47891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67714</t>
+          <t>66887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74693</t>
+          <t>73379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98134</t>
+          <t>98945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128424</t>
+          <t>128596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160476</t>
+          <t>159796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61892</t>
+          <t>63645</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82556</t>
+          <t>82876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64820</t>
+          <t>64977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89286</t>
+          <t>89805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134771</t>
+          <t>133691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165089</t>
+          <t>167031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16752</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>37565</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27604</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>31461</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57156</t>
+          <t>56388</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48023</t>
+          <t>47195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77576</t>
+          <t>76171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59949</t>
+          <t>59199</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90821</t>
+          <t>89540</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113489</t>
+          <t>113018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>157770</t>
+          <t>155181</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>243931</t>
+          <t>242288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>308440</t>
+          <t>308253</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>322697</t>
+          <t>325464</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>378834</t>
+          <t>381180</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>585507</t>
+          <t>588207</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>675994</t>
+          <t>674356</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>259970</t>
+          <t>258874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>336706</t>
+          <t>340129</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>290080</t>
+          <t>288335</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>347904</t>
+          <t>345296</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>564775</t>
+          <t>566757</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>661912</t>
+          <t>660400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A01_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25A01_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3192</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7422</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2955</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3274</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7807</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20646</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29786</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23429</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36574</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>52,95%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>41,65%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>65,01%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>27945</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>19147</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35779</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>54,77%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>37,53%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>70,13%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32758</t>
+          <t>22108</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25633</t>
+          <t>16512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>27580</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>60703</t>
+          <t>51893</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50127</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72393</t>
+          <t>60902</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16913</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11222</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23370</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,95%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12837</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7404</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18929</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18128</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>8408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25694</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30965</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40426</t>
+          <t>37853</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>38,0%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>51020</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>51020</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51020</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8720</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>15540</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>17708</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>11168</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30209</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>26874</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18845</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>41413</t>
+          <t>32692</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47836</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37710</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60416</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>38877</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28456</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50586</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>38019</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>29127</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>47849</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8,9%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>85855</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>71220</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>100172</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>11,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>50967</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>39271</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>64674</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>12,55%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>89844</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>75758</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>107586</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -1515,107 +1515,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>220648</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>198107</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>241959</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>197355</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>158501</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>218109</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>198670</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>181717</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>216216</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>46,53%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>42,56%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>50,64%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>419318</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>390943</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>450244</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>46,5%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>43,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,92%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>233641</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>209278</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>258504</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>45,32%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>40,6%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>50,15%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>430996</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>388866</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>462496</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>44,4%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>40,06%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>197526</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>175825</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>220849</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>41,61%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>37,04%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>46,52%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>201255</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>178371</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>246932</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>44,21%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>39,19%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>54,25%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>221706</t>
+          <t>175858</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>199336</t>
+          <t>158886</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>248359</t>
+          <t>194601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>422961</t>
+          <t>373384</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>388347</t>
+          <t>347251</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>474742</t>
+          <t>400031</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>474730</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>474730</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>474730</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>637</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>455195</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>455195</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>455195</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>515480</t>
+          <t>426993</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>515480</t>
+          <t>426993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>515480</t>
+          <t>426993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>970675</t>
+          <t>901723</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>970675</t>
+          <t>901723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>970675</t>
+          <t>901723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4784</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10544</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5899</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2899</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11619</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18176</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14125</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22332</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12290</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>7421</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>18822</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>26476</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>37498</t>
+          <t>36938</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>79440</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>68372</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>91325</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>40,6%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>54,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>57406</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>47891</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>66887</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38,66%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>86268</t>
+          <t>58099</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73379</t>
+          <t>47812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98945</t>
+          <t>68302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>143675</t>
+          <t>137539</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128596</t>
+          <t>123396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159796</t>
+          <t>153738</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,43%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>70069</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>59408</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>81077</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>72876</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>63645</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>82876</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>49,08%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>42,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>55,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>77194</t>
+          <t>72431</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64977</t>
+          <t>62278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89805</t>
+          <t>82021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>150070</t>
+          <t>142500</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133691</t>
+          <t>127380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>167031</t>
+          <t>157705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>148472</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>148472</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>148472</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>331821</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>331821</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>331821</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16697</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>10396</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>25550</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>24259</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>16933</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>37565</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>30040</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>41773</t>
+          <t>38054</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31461</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56388</t>
+          <t>49394</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>68328</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>55354</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>83056</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>60753</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>47195</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>76171</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>73045</t>
+          <t>57564</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59199</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89540</t>
+          <t>72528</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>133798</t>
+          <t>125892</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113018</t>
+          <t>109170</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>155181</t>
+          <t>145028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>329874</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>302197</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>353176</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>47,16%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>43,21%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>50,5%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>405</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>282706</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>242288</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>308253</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>43,18%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>37,01%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>47,08%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>352667</t>
+          <t>278876</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>325464</t>
+          <t>257468</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>381180</t>
+          <t>299818</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>635374</t>
+          <t>608750</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>588207</t>
+          <t>577541</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>674356</t>
+          <t>641381</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>286968</t>
+          <t>284509</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>258874</t>
+          <t>258578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>340129</t>
+          <t>312152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>317028</t>
+          <t>261577</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>288335</t>
+          <t>240577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>345296</t>
+          <t>282406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>603997</t>
+          <t>546085</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>566757</t>
+          <t>512797</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>660400</t>
+          <t>578505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>654687</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>654687</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>654687</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619375</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619375</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619375</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1414942</t>
+          <t>1318781</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1414942</t>
+          <t>1318781</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1414942</t>
+          <t>1318781</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
